--- a/Backend/employee_data.xlsx
+++ b/Backend/employee_data.xlsx
@@ -610,15 +610,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -644,10 +647,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>WORKING_HOURS</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>OT_HOURS</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>OT</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>CREATED_AT</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>UPDATED_AT</t>
         </is>
@@ -666,22 +684,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-11-10 09:00:00</t>
+          <t>2025-11-11 09:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-10 17:00:00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2025-11-10 22:25:11</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2025-11-10 22:25:11</t>
+          <t>2025-11-11 20:00:00</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2025-11-11 12:19:47</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2025-11-11 12:19:47</t>
         </is>
       </c>
     </row>
@@ -698,54 +727,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-11-10 09:00:00</t>
+          <t>2025-11-11 09:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-10 20:00:00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2025-11-10 22:26:36</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2025-11-10 22:26:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EMP001</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Phil dunphy</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2025-11-10 09:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2025-11-10 17:00:00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2025-11-10 22:32:17</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2025-11-10 22:32:17</t>
+          <t>2025-11-11 22:00:00</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2025-11-11 12:42:18</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2025-11-11 12:42:18</t>
         </is>
       </c>
     </row>
